--- a/lab-standards/LFMEAB-lab-standard.xlsx
+++ b/lab-standards/LFMEAB-lab-standard.xlsx
@@ -564,6 +564,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -577,6 +581,10 @@
 Workshop/Lab : 800-1000 sq. ft.</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -646,7 +654,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>9</v>
       </c>
@@ -668,7 +678,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>9</v>
       </c>
@@ -690,7 +702,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -712,7 +726,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -734,7 +750,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -756,7 +774,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -778,7 +798,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -800,7 +822,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -822,7 +846,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -844,7 +870,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>7</v>
       </c>
@@ -866,7 +894,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -888,7 +918,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>9</v>
       </c>
@@ -910,7 +942,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>9</v>
       </c>
@@ -932,7 +966,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>7</v>
       </c>
@@ -954,7 +990,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -976,7 +1014,9 @@
       <c r="C31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>8</v>
       </c>
@@ -998,7 +1038,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -1020,7 +1062,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -1166,6 +1210,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1179,6 +1227,10 @@
 Workshop : 800-1000 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1248,7 +1300,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>9</v>
       </c>
@@ -1270,7 +1324,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>9</v>
       </c>
@@ -1292,7 +1348,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -1314,7 +1372,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -1336,7 +1396,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -1358,7 +1420,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -1380,7 +1444,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -1402,7 +1468,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -1424,7 +1492,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -1446,7 +1516,9 @@
       <c r="C25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>8</v>
       </c>
@@ -1468,7 +1540,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -1490,7 +1564,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>8</v>
       </c>
@@ -1512,7 +1588,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -1534,7 +1612,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -1556,7 +1636,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -1578,7 +1660,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>5</v>
       </c>
@@ -1600,7 +1684,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -1622,7 +1708,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -1768,6 +1856,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1783,6 +1875,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1852,7 +1948,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -1874,7 +1972,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1896,7 +1996,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -1918,7 +2020,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -1940,7 +2044,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>3</v>
       </c>
@@ -1962,7 +2068,9 @@
       <c r="C21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -1984,7 +2092,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -2006,7 +2116,9 @@
       <c r="C23" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>3</v>
       </c>
@@ -2028,7 +2140,9 @@
       <c r="C24" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -2050,7 +2164,9 @@
       <c r="C25" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>10</v>
       </c>
@@ -2072,7 +2188,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -2094,7 +2212,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>9</v>
       </c>
@@ -2116,7 +2236,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -2138,7 +2260,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>3</v>
       </c>
@@ -2160,7 +2284,9 @@
       <c r="C30" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>4</v>
       </c>
@@ -2182,7 +2308,9 @@
       <c r="C31" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
@@ -2204,7 +2332,9 @@
       <c r="C32" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>4</v>
       </c>
@@ -2226,7 +2356,9 @@
       <c r="C33" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>4</v>
       </c>
@@ -2248,7 +2380,9 @@
       <c r="C34" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -2394,6 +2528,10 @@
           <t>SICIP required space for 20 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2408,6 +2546,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2477,7 +2619,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2499,7 +2643,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2521,7 +2667,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -2543,7 +2691,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -2565,7 +2715,9 @@
       <c r="C20" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>4</v>
       </c>
@@ -2587,7 +2739,9 @@
       <c r="C21" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -2609,7 +2763,9 @@
       <c r="C22" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -2631,7 +2787,9 @@
       <c r="C23" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -2653,7 +2811,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -2675,7 +2835,9 @@
       <c r="C25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -2697,7 +2859,9 @@
       <c r="C26" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -2719,7 +2883,9 @@
       <c r="C27" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>
@@ -2865,6 +3031,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2879,6 +3049,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2948,7 +3122,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2970,7 +3146,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2992,7 +3170,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -3014,7 +3194,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -3036,7 +3218,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -3058,7 +3242,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -3080,7 +3266,9 @@
       <c r="C22" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -3102,7 +3290,9 @@
       <c r="C23" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -3124,7 +3314,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -3146,7 +3338,9 @@
       <c r="C25" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>3</v>
       </c>
@@ -3168,7 +3362,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -3314,6 +3510,10 @@
           <t>SICIP required space for 20 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3328,6 +3528,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3397,7 +3601,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -3419,7 +3625,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -3441,7 +3649,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -3463,7 +3673,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -3485,7 +3697,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>3</v>
       </c>
@@ -3507,7 +3721,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -3529,7 +3745,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -3551,7 +3769,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -3573,7 +3793,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -3719,6 +3941,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3734,6 +3960,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3803,7 +4033,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -3825,7 +4057,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -3847,7 +4081,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -3869,7 +4105,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -3891,7 +4129,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -3911,7 +4151,9 @@
         </is>
       </c>
       <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -3937,7 +4179,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -3963,7 +4207,9 @@
       <c r="C23" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -3985,7 +4231,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -4007,7 +4255,9 @@
       <c r="C25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -4029,7 +4279,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -4051,7 +4303,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -4073,7 +4327,9 @@
       <c r="C28" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -4095,7 +4351,9 @@
       <c r="C29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -4117,7 +4375,9 @@
       <c r="C30" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>4</v>
       </c>
@@ -4139,7 +4399,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -4161,7 +4423,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>4</v>
       </c>
@@ -4307,6 +4571,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -4321,6 +4589,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4390,7 +4662,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -4412,7 +4686,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -4434,7 +4710,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -4456,7 +4734,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -4476,7 +4756,9 @@
         </is>
       </c>
       <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -4502,7 +4784,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -4528,7 +4812,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -4550,7 +4836,9 @@
       <c r="C23" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -4572,7 +4860,9 @@
       <c r="C24" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -4594,7 +4884,9 @@
       <c r="C25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -4616,7 +4908,9 @@
       <c r="C26" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -4638,7 +4932,9 @@
       <c r="C27" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -4660,7 +4956,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -4686,7 +4984,9 @@
       <c r="C29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>3</v>
       </c>
@@ -4708,7 +5008,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>4</v>
       </c>
@@ -4730,7 +5032,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -4752,7 +5056,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>4</v>
       </c>
@@ -4774,7 +5080,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>4</v>
       </c>
@@ -4920,6 +5228,10 @@
           <t>SICIP required space for 20 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -4934,6 +5246,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -5003,7 +5319,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -5025,7 +5343,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -5047,7 +5367,9 @@
       <c r="C18" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -5069,7 +5391,9 @@
       <c r="C19" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -5091,7 +5415,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -5113,7 +5439,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -5135,7 +5463,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -5161,7 +5491,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -5187,7 +5519,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -5213,7 +5547,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -5235,7 +5571,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -5257,7 +5595,9 @@
       <c r="C27" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -5279,7 +5619,9 @@
       <c r="C28" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -5301,7 +5643,9 @@
       <c r="C29" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>3</v>
       </c>
@@ -5323,7 +5667,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>5</v>
       </c>
@@ -5345,7 +5691,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>7</v>
       </c>
@@ -5367,7 +5715,9 @@
       <c r="C32" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
